--- a/artfynd/A 49709-2025 artfynd.xlsx
+++ b/artfynd/A 49709-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>477881</v>
       </c>
       <c r="B2" t="n">
-        <v>93374</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752972.9557473994</v>
+        <v>752973</v>
       </c>
       <c r="R2" t="n">
-        <v>6433414.703213074</v>
+        <v>6433415</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2009-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,12 +781,7 @@
         <v>1550729</v>
       </c>
       <c r="B3" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753093.2429191067</v>
+        <v>753093</v>
       </c>
       <c r="R3" t="n">
-        <v>6433543.07395605</v>
+        <v>6433543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,19 +846,9 @@
           <t>2002-03-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2002-03-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,12 +888,7 @@
         <v>75282583</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753092.7840099887</v>
+        <v>753093</v>
       </c>
       <c r="R4" t="n">
-        <v>6433415.921244553</v>
+        <v>6433416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,19 +956,9 @@
           <t>1996-10-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1996-10-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,6 +993,564 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117492984</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Raudstainsandet, S om vägen. Ringvida 1:5., Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>753042</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6433653</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fårö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kjell Mathson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kjell Mathson, Katarina Mathson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>56003071</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>N. Kullakärr, 400m V., Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>752874</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6433569</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fårö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2010-10-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2010-10-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>dike i lövskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kjell Mathson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kjell Mathson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>75941025</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norra Kullakärr, 300m V., Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>752881</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6433573</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fårö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2013-12-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2013-12-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>återfynd</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kjell Mathson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kjell Mathson, Jerker Mathson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>106387134</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stora Gasmora 900 m ONO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>753169</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6433727</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fårö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1983-01-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1984-12-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>.  Lassor 1:2</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gräsbevuxen sanddyn, basen av, med rörligt grundvatten där dynen övergår i odlingsmark.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gösta Fåhraeus</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112561024</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104283</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222075</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk dunört</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Epilobium obscurum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norra Kullakärr 300m VSV,, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>752979</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6433635</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fårö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rapporterat av Gösta Fåhraeus från samma lokal 1975  ( hans mark)</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>f.d. slåttervall och  lammbete</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kjell Mathson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kjell Mathson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49709-2025 artfynd.xlsx
+++ b/artfynd/A 49709-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/477881</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1550729</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75282583</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492984</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56003071</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75941025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106387134</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,8 +1591,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112561024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>